--- a/data/resampling-and-simulation--salaries.xlsx
+++ b/data/resampling-and-simulation--salaries.xlsx
@@ -6015,14 +6015,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WHAT IS CAPTURED: an HR compensation export.</t>
+          <t>WHAT IS CAPTURED: an HR compensation export (a realistic teaching dataset written for the book).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Goal: a confidence interval for the MEDIAN salary - there is no simple formula, so we BOOTSTRAP.</t>
+          <t>Goal: a confidence interval for the MEDIAN salary. It has no simple standard-error formula, so we BOOTSTRAP (and compare the exact order-statistic interval).</t>
         </is>
       </c>
     </row>
